--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/TestPlans/BIBS_TestPlan_BRD-03_Product_Maintenance_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/TestPlans/BIBS_TestPlan_BRD-03_Product_Maintenance_v1.0.xlsx
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Demo users of TD-PM-01 are active; the audit trail is empty for the test period.</t>
+          <t>SIT/UAT users of TD-PM-01 are active; the audit trail is empty for the test period.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -7975,13 +7975,13 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
           <t>1. Open the BIBS URL.
-2. Enter user ID ao and the demo password; click Sign in.
+2. Enter user ID ao and The SIT/UAT password; click Sign in.
 3. Open the side menu.</t>
         </is>
       </c>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -8204,7 +8204,7 @@
       <c r="I8" s="12" t="inlineStr">
         <is>
           <t>Administration &gt; System Parameters shows LOGIN_MAX_FAILED_ATTEMPTS (3 as delivered).
-Data: TD-PM-01 Demo users and roles</t>
+Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -8360,7 +8360,7 @@
       <c r="I10" s="12" t="inlineStr">
         <is>
           <t>Cases TC-PM-001.1-01 and TC-PM-001.2-01 ran today.
-Data: TD-PM-01 Demo users and roles</t>
+Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>ProductMaintenanceFoundationIT#demoPersonasHoldTheirProductMaintenancePermissions</t>
+          <t>ProductMaintenanceFoundationIT#seedPersonasHoldTheirProductMaintenancePermissions</t>
         </is>
       </c>
       <c r="N11" s="27" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -8984,7 +8984,7 @@
       <c r="I18" s="12" t="inlineStr">
         <is>
           <t>A test user holding ACCESS_REQUEST and ACCESS_APPROVE (set up by the test lead for this case) submitted a Modify role permissions request.
-Data: TD-PM-01 Demo users and roles</t>
+Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 Demo users and roles</t>
+          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -9216,7 +9216,7 @@
       <c r="I21" s="12" t="inlineStr">
         <is>
           <t>badmin submitted a request to remove PRODUCT_VIEW from AUDITOR.
-Data: TD-PM-01 Demo users and roles</t>
+Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -9294,7 +9294,7 @@
       <c r="I22" s="12" t="inlineStr">
         <is>
           <t>TC-PM-003.1-01 is done.
-Data: TD-PM-01 Demo users and roles</t>
+Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>A user holding only a non-broking role (for example a GL user of the finance demo) exists.
+          <t>A user holding only a non-broking role (for example a GL user of the finance seed) exists.
 Data: TD-PM-04 Client-specific request in negotiation; TD-PM-11 Catalogue and insurer panel</t>
         </is>
       </c>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
-          <t>ProductMaintenanceApiIT#aDemoRequestIsReadableWithItsRoundsOutputsAndDocuments</t>
+          <t>ProductMaintenanceApiIT#aSeedRequestIsReadableWithItsRoundsOutputsAndDocuments</t>
         </is>
       </c>
       <c r="N48" s="27" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
@@ -13457,7 +13457,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H94" s="12" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="M100" s="12" t="inlineStr">
         <is>
-          <t>ProductMaintenanceApiIT#aDemoRequestIsReadableWithItsRoundsOutputsAndDocuments</t>
+          <t>ProductMaintenanceApiIT#aSeedRequestIsReadableWithItsRoundsOutputsAndDocuments</t>
         </is>
       </c>
       <c r="N100" s="27" t="inlineStr">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
@@ -15643,7 +15643,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H115" s="12" t="inlineStr">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
@@ -16839,7 +16839,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>MANCOM – ManCom member (demo user mancom)</t>
+          <t>MANCOM – ManCom member (SIT/UAT user mancom)</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>PackageRequestProcessIT#aNewPackageRunsFromDraftToReleasedWithTwoRoundsAndAnAdvisory; ProductMaintenanceApiIT#aDemoRequestIsReadableWithItsRoundsOutputsAndDocuments</t>
+          <t>PackageRequestProcessIT#aNewPackageRunsFromDraftToReleasedWithTwoRoundsAndAnAdvisory; ProductMaintenanceApiIT#aSeedRequestIsReadableWithItsRoundsOutputsAndDocuments</t>
         </is>
       </c>
       <c r="N131" s="27" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>MANCOM – ManCom member (demo user mancom)</t>
+          <t>MANCOM – ManCom member (SIT/UAT user mancom)</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -17831,7 +17831,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>MANCOM – ManCom member (demo user mancom)</t>
+          <t>MANCOM – ManCom member (SIT/UAT user mancom)</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -17905,7 +17905,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>MANCOM – ManCom member (demo user mancom)</t>
+          <t>MANCOM – ManCom member (SIT/UAT user mancom)</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
@@ -17977,7 +17977,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
@@ -18127,7 +18127,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -18425,7 +18425,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H147" s="12" t="inlineStr">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
@@ -19178,7 +19178,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
@@ -19272,7 +19272,7 @@
       <c r="J154" s="12" t="inlineStr">
         <is>
           <t>1. Upload the signed package slip.
-2. Edit the advisory - groups Marketing and Operations, e-mail operations@brokerverse-demo.ph, subject "MTR15 renewed", text; save.
+2. Edit the advisory - groups Marketing and Operations, e-mail operations@brokerverse-seed.ph, subject "MTR15 renewed", text; save.
 3. Click Send. As ao open the notification bell.</t>
         </is>
       </c>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
@@ -19787,7 +19787,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H166" s="12" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H169" s="12" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H173" s="12" t="inlineStr">
@@ -20775,7 +20775,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
@@ -20852,7 +20852,7 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H175" s="12" t="inlineStr">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H178" s="12" t="inlineStr">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H180" s="12" t="inlineStr">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H181" s="12" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H182" s="12" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H183" s="12" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H184" s="12" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H185" s="12" t="inlineStr">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H186" s="12" t="inlineStr">
@@ -21753,7 +21753,7 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H188" s="12" t="inlineStr">
@@ -21906,7 +21906,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H191" s="12" t="inlineStr">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H192" s="12" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H195" s="12" t="inlineStr">
@@ -22429,7 +22429,7 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H196" s="12" t="inlineStr">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H197" s="12" t="inlineStr">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H198" s="12" t="inlineStr">
@@ -22657,7 +22657,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr">
@@ -22730,7 +22730,7 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H200" s="12" t="inlineStr">
@@ -22807,7 +22807,7 @@
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H201" s="12" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H202" s="12" t="inlineStr">
@@ -22959,7 +22959,7 @@
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H203" s="12" t="inlineStr">
@@ -23031,7 +23031,7 @@
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H205" s="12" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H206" s="12" t="inlineStr">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -23333,7 +23333,7 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H208" s="12" t="inlineStr">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H210" s="12" t="inlineStr">
@@ -23501,7 +23501,7 @@
       </c>
       <c r="J210" s="12" t="inlineStr">
         <is>
-          <t>1. Click New Criterion; code UAT1, name "UAT campaign", type Sales campaign (demo), value basis Fixed amount, value 500, effective from today; products MTR12; save.
+          <t>1. Click New Criterion; code UAT1, name "UAT campaign", type Sales campaign (seed), value basis Fixed amount, value 500, effective from today; products MTR12; save.
 2. As badmin authorise it in My Approvals.</t>
         </is>
       </c>
@@ -23563,7 +23563,7 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H211" s="12" t="inlineStr">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H212" s="12" t="inlineStr">
@@ -23717,7 +23717,7 @@
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H213" s="12" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H214" s="12" t="inlineStr">
@@ -23867,7 +23867,7 @@
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H215" s="12" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H216" s="12" t="inlineStr">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H217" s="12" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H218" s="12" t="inlineStr">
@@ -24167,7 +24167,7 @@
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H219" s="12" t="inlineStr">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H220" s="12" t="inlineStr">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H222" s="12" t="inlineStr">
@@ -24472,7 +24472,7 @@
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H223" s="12" t="inlineStr">
@@ -24549,7 +24549,7 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H224" s="12" t="inlineStr">
@@ -27663,17 +27663,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Demo users and roles</t>
+          <t>SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>ao and ao2 (MKT_AO), mkttl (MKT_TL), tsu (TSU), tsulead (TSU and TSU_TL), tsuhead (TSU_HEAD), mbs and mbs2 (MBS), mancom (MANCOM), badmin (BUSINESS_ADMIN), approver (NB_APPROVER), admin (SYSADMIN), auditor (AUDITOR). The demo password is issued by the test lead.</t>
+          <t>ao and ao2 (MKT_AO), mkttl (MKT_TL), tsu (TSU), tsulead (TSU and TSU_TL), tsuhead (TSU_HEAD), mbs and mbs2 (MBS), mancom (MANCOM), badmin (BUSINESS_ADMIN), approver (NB_APPROVER), admin (SYSADMIN), auditor (AUDITOR). The SIT/UAT password is issued by the test lead.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V980 (broking users), V998 (Product Maintenance users), V900 (admin, auditor); roles and grants V755</t>
+          <t>Seeds V980 (broking users), V998 (Product Maintenance users), V900 (admin, auditor); roles and grants V755</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V997</t>
+          <t>Seed V997</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V997</t>
+          <t>Seed V997</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V997</t>
+          <t>Seed V997</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
@@ -27773,7 +27773,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V997</t>
+          <t>Seed V997</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V997</t>
+          <t>Seed V997</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -27823,7 +27823,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V997</t>
+          <t>Seed V997</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V996</t>
+          <t>Seed V996</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -27868,12 +27868,12 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>CPC2 (demo), type CAMPAIGN, value basis RATE 1.00, on Motor and Property packages, ACTIVE</t>
+          <t>CPC2 (seed), type CAMPAIGN, value basis RATE 1.00, on Motor and Property packages, ACTIVE</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V996</t>
+          <t>Seed V996</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
@@ -27898,7 +27898,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V996</t>
+          <t>Seed V996</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -27923,7 +27923,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V981 (clients), V982 (catalogue), V996 (versions)</t>
+          <t>Seeds V981 (clients), V982 (catalogue), V996 (versions)</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V981 and V984; for UAT a masked copy of production-like data</t>
+          <t>Seeds V981 and V984; for UAT a masked copy of production-like data</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
@@ -28172,7 +28172,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -28223,7 +28223,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -28325,7 +28325,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -28376,7 +28376,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>MANCOM – ManCom member (demo user mancom)</t>
+          <t>MANCOM – ManCom member (SIT/UAT user mancom)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -28427,7 +28427,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -28478,7 +28478,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -28580,7 +28580,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -28631,7 +28631,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -28682,7 +28682,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -28776,7 +28776,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -28823,7 +28823,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -28917,7 +28917,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -29011,7 +29011,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -29058,7 +29058,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -29152,7 +29152,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -29199,7 +29199,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -29293,7 +29293,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -29446,7 +29446,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>MANCOM – ManCom member (demo user mancom)</t>
+          <t>MANCOM – ManCom member (SIT/UAT user mancom)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -29497,7 +29497,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -29548,7 +29548,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -29701,7 +29701,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -29752,7 +29752,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -29803,7 +29803,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -29956,7 +29956,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -30007,7 +30007,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -30058,7 +30058,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -30109,7 +30109,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (demo user tsulead)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -30262,7 +30262,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -30364,7 +30364,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -30415,7 +30415,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -30466,7 +30466,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -30517,7 +30517,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -30619,7 +30619,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -30670,7 +30670,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -30721,7 +30721,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -30772,7 +30772,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -30823,7 +30823,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -30874,7 +30874,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -30925,7 +30925,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -30976,7 +30976,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -31023,7 +31023,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -31117,7 +31117,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -31211,7 +31211,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -31258,7 +31258,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -31352,7 +31352,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (demo user tsuhead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -31399,7 +31399,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (demo user mbs)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -31446,7 +31446,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -31493,7 +31493,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -31540,7 +31540,7 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (demo user tsu)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
